--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.575577757849032</v>
+        <v>0.9060313856504677</v>
       </c>
       <c r="D2" t="n">
-        <v>22.56286211437728</v>
+        <v>3.666465093586309</v>
       </c>
       <c r="E2" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F2" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.38517797157454</v>
+        <v>1.850091420380863</v>
       </c>
       <c r="D3" t="n">
-        <v>11.93075133471106</v>
+        <v>1.938747091890548</v>
       </c>
       <c r="E3" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F3" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4.847395227747942</v>
+        <v>0.7877017245090406</v>
       </c>
       <c r="D4" t="n">
-        <v>15.65584799861217</v>
+        <v>2.544075299774478</v>
       </c>
       <c r="E4" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F4" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.280109889280518</v>
+        <v>1.183017857008084</v>
       </c>
       <c r="D5" t="n">
-        <v>25.01193957068863</v>
+        <v>4.064440180236902</v>
       </c>
       <c r="E5" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F5" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.35655495770978</v>
+        <v>2.82044018062784</v>
       </c>
       <c r="D6" t="n">
-        <v>15.12805001159607</v>
+        <v>2.458308126884361</v>
       </c>
       <c r="E6" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F6" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.20796143371138</v>
+        <v>2.633793732978099</v>
       </c>
       <c r="D7" t="n">
-        <v>11.11316709256291</v>
+        <v>1.805889652541472</v>
       </c>
       <c r="E7" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F7" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.71834935510066</v>
+        <v>3.366731770203857</v>
       </c>
       <c r="D8" t="n">
-        <v>31.27929343081241</v>
+        <v>5.082885182507016</v>
       </c>
       <c r="E8" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F8" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.0415945787923</v>
+        <v>1.956759119053748</v>
       </c>
       <c r="D9" t="n">
-        <v>21.78636674485287</v>
+        <v>3.540284596038591</v>
       </c>
       <c r="E9" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F9" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.82931668593933</v>
+        <v>2.247263961465142</v>
       </c>
       <c r="D10" t="n">
-        <v>12.14222610270083</v>
+        <v>1.973111741688884</v>
       </c>
       <c r="E10" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F10" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.020797289396148</v>
+        <v>0.9783795595268741</v>
       </c>
       <c r="D11" t="n">
-        <v>18.15302012276728</v>
+        <v>2.949865769949684</v>
       </c>
       <c r="E11" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F11" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.20223329492583</v>
+        <v>2.470362910425448</v>
       </c>
       <c r="D12" t="n">
-        <v>11.65712837603279</v>
+        <v>1.894283361105328</v>
       </c>
       <c r="E12" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F12" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>6.735765868714143</v>
+        <v>1.094561953666048</v>
       </c>
       <c r="D13" t="n">
-        <v>15.11606033436317</v>
+        <v>2.456359804334015</v>
       </c>
       <c r="E13" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F13" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.65641423364471</v>
+        <v>2.056667312967265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.54997531687745</v>
+        <v>2.364370988992586</v>
       </c>
       <c r="E14" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F14" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>19.84943324127921</v>
+        <v>3.225532901707871</v>
       </c>
       <c r="D15" t="n">
-        <v>29.54086646871296</v>
+        <v>4.800390801165856</v>
       </c>
       <c r="E15" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F15" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.96301130559871</v>
+        <v>6.006489337159791</v>
       </c>
       <c r="D16" t="n">
-        <v>47.28885585895546</v>
+        <v>7.684439077080263</v>
       </c>
       <c r="E16" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F16" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>9.159711300642133</v>
+        <v>1.488453086354347</v>
       </c>
       <c r="D17" t="n">
-        <v>74.21075032465383</v>
+        <v>12.05924692775625</v>
       </c>
       <c r="E17" t="n">
-        <v>7.795578224755926</v>
+        <v>1.266781461522838</v>
       </c>
       <c r="F17" t="n">
-        <v>16.02275390836208</v>
+        <v>2.603697510108838</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
